--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$198</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G197"/>
+  <dimension ref="A1:G198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6861,8 +6861,39 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Fences &amp; Railing for Sale in Tanta‏(4)</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>010013283, 010051109, 010056666, 010056990, 010062694, 010116275, 010171976, 010204002, 010283573, 010291214, 010302293, 010331668, 010500745, 010938115, 010990705, 011005642, 011112887, 011119939, 011129285, 011133800, 011166456, 011193244, 011421594, 011430686, 011450179, 011557141, 011581172, 012004185, 012024029, 012032250, 012231775, 012244660, 012258390, 012757567, 012780005, 012800488, 012842955, 012878499, 012880586, 012897347, 015518334</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr"/>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>https://eg.opensooq.com/en/tanta/home-garden/fences-and-railing</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>site:opensooq.com ابواب مصفحة مصر</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G197"/>
+  <autoFilter ref="A1:G198"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$198</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$199</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G198"/>
+  <dimension ref="A1:G199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6892,8 +6892,39 @@
         </is>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>فالي ميتال للابواب المعدنية</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>الاردن</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>202101110855</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr"/>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>https://www.valleymetaldoors.com/</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>معرض ابواب مصفحة عمان</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G198"/>
+  <autoFilter ref="A1:G199"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G199"/>
+  <dimension ref="A1:G201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6923,8 +6923,70 @@
         </is>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>أبواب أمان للبيع في مصر‏(10)</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>010065550, 010500745, 011005642, 011133800, 011421594</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr"/>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>https://eg.opensooq.com/ar/المنزل-والحديقة/أبواب-أمان</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>site:opensooq.com ابواب مصفحة مصر</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>إكسسوارات الشبابيك للبيع في مصر‏(2)</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>010013283, 010056666, 010062694, 010065550, 010116275, 010171976, 010204002, 010237719, 010269913, 010291214, 010302293, 010331668, 010367247, 010500745, 010938115, 010990705, 011005642, 011112887, 011119939, 011129285, 011133800, 011193244, 011245058, 011421594, 011430686, 011500620, 012004185, 012024029, 012231775, 012244660, 012258390, 012757567, 012771637, 012780005, 012800488, 012820776, 012842955, 012878499, 012892558, 012897347, 015150771</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr"/>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>https://eg.opensooq.com/ar/المنزل-والحديقة/إكسسوارات-الشبابيك</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>site:opensooq.com ابواب مصفحة مصر</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G199"/>
+  <autoFilter ref="A1:G201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$202</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G201"/>
+  <dimension ref="A1:G202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6985,8 +6985,43 @@
         </is>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>About Imported Steel Doors Kenya</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>254716704836</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>info@steeldoorskenya.co.ke</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>https://steeldoorskenya.co.ke/</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer ghana nigeria kenya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G201"/>
+  <autoFilter ref="A1:G202"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$203</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G202"/>
+  <dimension ref="A1:G203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7020,8 +7020,39 @@
         </is>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Fire Rated Doors &amp; Emergency Doors</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>201039713471</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr"/>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>https://beta-metal.com/our-products</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer egypt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G202"/>
+  <autoFilter ref="A1:G203"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$204</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G203"/>
+  <dimension ref="A1:G204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7051,8 +7051,39 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Ufukta harika şeyler var</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>عام</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>05496858095, 905496858095</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr"/>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>https://ozkuvvetalci.com/urun/turkish-steel-door-supplier-exporter-wholesale-doo</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>wholesale steel door turkey exporter</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G203"/>
+  <autoFilter ref="A1:G204"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$205</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G204"/>
+  <dimension ref="A1:G205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7082,8 +7082,39 @@
         </is>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>إكسسوارات الأبواب للبيع في العراق‏(15)</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>العراق</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>075046505, 077027895, 077032859, 077041890, 077056160, 077056925, 077063251, 077068971, 077077577, 077086826, 077119202, 077131198, 077132306, 077140666, 077162920, 077163073, 077182671, 077191891, 077212893, 077228871, 077261182, 077261889, 077281106, 077295083, 077304772, 077326882, 077330007, 077337779, 077338889, 077366386, 077380913, 077383722, 077399714, 077412129, 077602708, 077635027, 077838334, 078013174, 078014166, 078028021, 078158879, 078188326, 078281599, 078315103, 078382964, 07838</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr"/>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>https://iq.opensooq.com/ar/المنزل-والحديقة/إكسسوارات-الأبواب</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>اسعار الابواب المصفحة في العراق</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G204"/>
+  <autoFilter ref="A1:G205"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$206</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G205"/>
+  <dimension ref="A1:G206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7113,8 +7113,39 @@
         </is>
       </c>
     </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>أبواب داخلية للبيع في العراق‏(112)</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>العراق</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>077005068, 077041890, 077055385, 077056160, 077062697, 077077577, 077101823, 077182671, 077191891, 077261889, 077295083, 077383722, 077448929, 077626236, 077651703, 077805063, 078020515, 078166639, 078188326, 078281599, 078315103, 078439978, 078666776, 078745415, 078750574, 078791692, 078809558</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr"/>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>https://iq.opensooq.com/ar/المنزل-والحديقة/أبواب-داخلية</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>اسعار الابواب المصفحة في العراق</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G205"/>
+  <autoFilter ref="A1:G206"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$208</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G206"/>
+  <dimension ref="A1:G208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7144,8 +7144,74 @@
         </is>
       </c>
     </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>China Leading Factory Exporting Africa Popular Design Tank Doors 2050*960*90 Ste</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>18587696286, 377727587, 8613557317112, 8618587696, 8618587696286</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>catherine@zonledoors.com</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.zonledoors.com/china-leading-factory-exporting-africa-popular-design</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>safety door supplier west africa</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>باب تركي كامل بالاكسسوارات</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>ليبيا</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>2189164303, 286003616</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr"/>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>https://ly.opensooq.com/ar/search/286003616</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>باب مصفح تركي للبيع في ليبيا</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G206"/>
+  <autoFilter ref="A1:G208"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$208</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$209</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G208"/>
+  <dimension ref="A1:G209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7210,8 +7210,43 @@
         </is>
       </c>
     </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>About Us - Medico Steel Door</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>201005431710, 201010777095, 201094758888</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>info@medicosteeldoor.com, sales@medicosteeldoor.com</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>https://medicosteeldoor.com/about-us/</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer egypt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G208"/>
+  <autoFilter ref="A1:G209"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$210</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G209"/>
+  <dimension ref="A1:G210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7245,8 +7245,39 @@
         </is>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>imported door locks suppliers</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>010185195126</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr"/>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.alibaba.com/imported-door-locks-suppliers.html</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>site:alibaba.com steel door africa importer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G209"/>
+  <autoFilter ref="A1:G210"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$210</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$211</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G210"/>
+  <dimension ref="A1:G211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7276,8 +7276,43 @@
         </is>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 Leading Door Hardware Brands in Morocco: A Comprehensive Guide - umaylock</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>المغرب</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>8615370347898</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>umay@umaylock.com</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>https://umaylocks.com/top-10-leading-door-hardware-brands-in-morocco/</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer morocco</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G210"/>
+  <autoFilter ref="A1:G211"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$212</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G211"/>
+  <dimension ref="A1:G212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7311,8 +7311,39 @@
         </is>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>Africa Door Factory Manufacturers &amp; Suppliers</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>1925011000, 562201500</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr"/>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.made-in-china.com/manufacturers/africa-door-factory.html</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>armored door supplier south africa kenya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G211"/>
+  <autoFilter ref="A1:G212"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$212</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$213</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G212"/>
+  <dimension ref="A1:G213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7342,8 +7342,39 @@
         </is>
       </c>
     </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>أربيل، العراق - معرض صناعة البناء، 23 سبتمبر 2025 حول أبواب مقاومة للحريق</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>العراق</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>8613801977102</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr"/>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ulfiredoormfg.com/ar/-erbil-iraq-construction-industry-exhibitionsep</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>معرض ابواب في العراق</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G212"/>
+  <autoFilter ref="A1:G213"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$214</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G213"/>
+  <dimension ref="A1:G214"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7373,8 +7373,43 @@
         </is>
       </c>
     </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Doors &amp; Fire Rated Doors Manufacturer Since 2010</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>8618102249574</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>song@yesoondoor.com</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>https://yesoondoor.com/</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>fire door distributor senegal ivory coast</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G213"/>
+  <autoFilter ref="A1:G214"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$215</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G214"/>
+  <dimension ref="A1:G215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7408,8 +7408,39 @@
         </is>
       </c>
     </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>Africa Door Price Manufacturers &amp; Suppliers</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>1905011000, 567201500</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr"/>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.made-in-china.com/manufacturers/africa-door-price.html</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>armored door supplier south africa kenya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G214"/>
+  <autoFilter ref="A1:G215"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$215</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$216</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G215"/>
+  <dimension ref="A1:G216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7439,8 +7439,39 @@
         </is>
       </c>
     </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>Cameroon Market Steel Security Exterior Metal Entry Double Door</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>101270000, 12500100219</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr"/>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>https://m.made-in-china.com/product/Cameroon-Market-Steel-Security-Exterior-Meta</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>metal door dealer ghana nigeria cameroon</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G215"/>
+  <autoFilter ref="A1:G216"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$217</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G216"/>
+  <dimension ref="A1:G217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7470,8 +7470,43 @@
         </is>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>About Us</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>233207660961</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>info@doorslocksandmore.com</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>https://doorslocksandmore.com/about-us/</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>safety door supplier west africa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G216"/>
+  <autoFilter ref="A1:G217"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$218</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G217"/>
+  <dimension ref="A1:G218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7505,8 +7505,39 @@
         </is>
       </c>
     </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>steel doors qatar importers suppliers</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>العراق</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>010177051143, 971565478106, 9715677976760</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr"/>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.alibaba.com/steel-doors-qatar-importers-suppliers.html</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>steel door iraq importer</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G217"/>
+  <autoFilter ref="A1:G218"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$218</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$219</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G218"/>
+  <dimension ref="A1:G219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7536,8 +7536,43 @@
         </is>
       </c>
     </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>Hollow Metal Doors</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>المغرب</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>13235181223, 18443213667, 8443213667, 902483100</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>sales@usafiredoor.com</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/aclick?ld=e8LW7XoSeSEMeRnWlWK30AqzVUCUzvG3ZfehUTUnxObF97ak3</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer morocco</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G218"/>
+  <autoFilter ref="A1:G219"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$219</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$220</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G219"/>
+  <dimension ref="A1:G220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7571,8 +7571,39 @@
         </is>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>Iron Doors - Iron Entry Doors - Front Doors - Wrought Iron Entry Doors</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>2334805884811, 4803396145, 4809241104, 6023457533, 78735512524, 78735512662, 85209480339, 85233480588, 85254480339, 85340623433, 85701520834</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr"/>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bing.com/aclick?ld=e83oHLlHFCP8sEFH8jqmH8nDVUCUxSGotgzhh6-qnvyS98RJF</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>metal door importer tanzania ethiopia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G219"/>
+  <autoFilter ref="A1:G220"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$221</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G220"/>
+  <dimension ref="A1:G221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7602,8 +7602,39 @@
         </is>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>المغرب</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>875787588759, 876087618762, 876387648765</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr"/>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>https://construction.made-in-china.com/products/Door-8762.html</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer morocco</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G220"/>
+  <autoFilter ref="A1:G221"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$222</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G221"/>
+  <dimension ref="A1:G222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7633,8 +7633,43 @@
         </is>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>ZADPROTECT EGYPT</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>201227425, 201227425386, 20132714617</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>info@protectegypt.net, zad_co@yahoo.com</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>http://www.protectegypt.net/</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer egypt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G221"/>
+  <autoFilter ref="A1:G222"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$222</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$223</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G222"/>
+  <dimension ref="A1:G223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7668,8 +7668,39 @@
         </is>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>Doors Windows &amp; Gates for Sale in Egypt‏(68)</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>010002764, 010021911, 010040168, 010051109, 010053591, 010056990, 010157383, 010331668, 010358635, 010500745, 010610236, 011117881, 011128645, 011166575, 011190556, 011222519, 011418111, 011508357, 012034618, 012228674, 012270050, 012733780, 012842955, 012892558</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr"/>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>https://eg.opensooq.com/en/home-garden/doors-windows-aluminium</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>site:opensooq.com ابواب مصفحة مصر</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G222"/>
+  <autoFilter ref="A1:G223"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$223</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$224</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G223"/>
+  <dimension ref="A1:G224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7699,8 +7699,39 @@
         </is>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Doors in Jammu</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>9700318318</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr"/>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.exportersindia.com/jammu/doors.htm</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>site:exportersindia.com steel door africa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G223"/>
+  <autoFilter ref="A1:G224"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$224</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$225</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G224"/>
+  <dimension ref="A1:G225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7730,8 +7730,43 @@
         </is>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>Pyropanel Fire Doors</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>315637307</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>info@pelican.co.za</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.pelican.co.za/product-category/opening/fire-doors/</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>fire door distributor senegal ivory coast</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G224"/>
+  <autoFilter ref="A1:G225"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$227</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G225"/>
+  <dimension ref="A1:G227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7765,8 +7765,74 @@
         </is>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>أبواب أمان للبيع في الأردن‏(36)</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>الاردن</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>079949001</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr"/>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>https://jo.opensooq.com/ar/search/275264057</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>باب امان تركي الاردن معارض</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>Contact Us - Spintex Road Location</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>233270766662, 233509945002</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>safetyandhomesolutions@gmail.com</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sahsghana.com/pages/contact-us-safety-and-home-solutions-location</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>safety door supplier west africa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G225"/>
+  <autoFilter ref="A1:G227"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$227</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$228</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G227"/>
+  <dimension ref="A1:G228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7831,8 +7831,43 @@
         </is>
       </c>
     </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>Steel Doors</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>افريقيا</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>233303941914</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>info@dolphindoors.com</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dolphindoors.com/full-steel-doors</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>metal door dealer ghana nigeria cameroon</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G227"/>
+  <autoFilter ref="A1:G228"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$228</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$229</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G228"/>
+  <dimension ref="A1:G229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7866,8 +7866,39 @@
         </is>
       </c>
     </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>Steel Doors Egypt — certified door systems for every critical environment.</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>010038010160127</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr"/>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.realsteeldoorseg.com/catalog</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>steel door importer egypt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G228"/>
+  <autoFilter ref="A1:G229"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$229</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$230</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G229"/>
+  <dimension ref="A1:G230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7897,8 +7897,39 @@
         </is>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>باب تركي للبيع</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>ليبيا</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>288284806</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr"/>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>https://ly.opensooq.com/ar/search/288284806</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>باب مصفح تركي للبيع في ليبيا</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G229"/>
+  <autoFilter ref="A1:G230"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأرقام" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'الأرقام'!$A$1:$G$231</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G230"/>
+  <dimension ref="A1:G231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7928,8 +7928,39 @@
         </is>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>ابواب حديد مقاومة للحريق</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>مصر</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>01003221214, 2000225452230</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr"/>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>https://matrix-doors.co/ar/ابواب-حديد-مقاومة-للحريق/</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>تجار ابواب حديدية في مصر</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G230"/>
+  <autoFilter ref="A1:G231"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>